--- a/Vf/TABLE_4_5/Table_5_PanelC_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelC_MIDAS.xlsx
@@ -447,16 +447,16 @@
         <v>-0.9</v>
       </c>
       <c r="B2" t="n">
-        <v>1.11972974677082</v>
+        <v>1.119342037048865</v>
       </c>
       <c r="C2" t="n">
-        <v>1.104143098118585</v>
+        <v>1.103140983233255</v>
       </c>
       <c r="D2" t="n">
-        <v>1.101352629697872</v>
+        <v>1.100683472822697</v>
       </c>
       <c r="E2" t="n">
-        <v>1.152001362873217</v>
+        <v>1.151820457419298</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>-0.5</v>
       </c>
       <c r="B3" t="n">
-        <v>1.087429604967771</v>
+        <v>1.08716525590362</v>
       </c>
       <c r="C3" t="n">
-        <v>1.113955375762663</v>
+        <v>1.113931686771855</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117797668114778</v>
+        <v>1.118051709205421</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22798863308004</v>
+        <v>1.228161267403393</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1.080392546859021</v>
+        <v>1.080428143124784</v>
       </c>
       <c r="C4" t="n">
-        <v>1.115303339479359</v>
+        <v>1.11513026914421</v>
       </c>
       <c r="D4" t="n">
-        <v>1.13195120529391</v>
+        <v>1.131715629231821</v>
       </c>
       <c r="E4" t="n">
-        <v>1.233636052886394</v>
+        <v>1.233536151023955</v>
       </c>
     </row>
     <row r="5">
@@ -501,13 +501,13 @@
         <v>1.084430333703487</v>
       </c>
       <c r="C5" t="n">
-        <v>1.122299670469697</v>
+        <v>1.121902516602085</v>
       </c>
       <c r="D5" t="n">
-        <v>1.134418897652784</v>
+        <v>1.134124623876767</v>
       </c>
       <c r="E5" t="n">
-        <v>1.23944290654707</v>
+        <v>1.239312507525674</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>1.190387160660586</v>
+        <v>1.186753117367767</v>
       </c>
       <c r="C6" t="n">
-        <v>1.288393548933058</v>
+        <v>1.283318823683066</v>
       </c>
       <c r="D6" t="n">
-        <v>1.29568626346573</v>
+        <v>1.29421844582944</v>
       </c>
       <c r="E6" t="n">
-        <v>1.312781083967614</v>
+        <v>1.311472257145955</v>
       </c>
     </row>
   </sheetData>
